--- a/accountant-skill/data/output/Jan2026/bank_reconciliation_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/bank_reconciliation_Jan2026.xlsx
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -136,11 +136,39 @@
     <border>
       <bottom style="double"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -188,6 +216,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,14 +606,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="33" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -596,21 +644,28 @@
           <t>RECONCILIATION STATUS</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="22" t="n"/>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="23" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>RECONCILED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -621,14 +676,21 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="24" t="inlineStr">
         <is>
           <t>BALANCES</t>
         </is>
       </c>
+      <c r="B9" s="22" t="n"/>
+      <c r="C9" s="22" t="n"/>
+      <c r="D9" s="22" t="n"/>
+      <c r="E9" s="22" t="n"/>
+      <c r="F9" s="22" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>Cash Book Closing Balance</t>
         </is>
@@ -638,7 +700,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="8" t="inlineStr">
         <is>
           <t>Bank Statement Closing Balance</t>
         </is>
@@ -648,7 +710,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Adjusted Book Balance</t>
         </is>
@@ -658,7 +720,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="8" t="inlineStr">
         <is>
           <t>Adjusted Bank Balance</t>
         </is>
@@ -669,82 +731,96 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="24" t="inlineStr">
         <is>
           <t>RECONCILING ITEMS</t>
         </is>
       </c>
+      <c r="B15" s="22" t="n"/>
+      <c r="C15" s="22" t="n"/>
+      <c r="D15" s="22" t="n"/>
+      <c r="E15" s="22" t="n"/>
+      <c r="F15" s="22" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>Transactions Matched</t>
         </is>
       </c>
-      <c r="B16" s="8" t="n">
+      <c r="B16" s="7" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>Deposits in Transit</t>
         </is>
       </c>
-      <c r="B17" s="8" t="n">
+      <c r="B17" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="8" t="inlineStr">
         <is>
           <t>Outstanding Cheques</t>
         </is>
       </c>
-      <c r="B18" s="8" t="n">
+      <c r="B18" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>Bank Credits not in Book</t>
         </is>
       </c>
-      <c r="B19" s="8" t="n">
+      <c r="B19" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>Bank Debits not in Book</t>
         </is>
       </c>
-      <c r="B20" s="8" t="n">
+      <c r="B20" s="7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Adjusting Entries Required</t>
         </is>
       </c>
-      <c r="B21" s="8" t="n">
+      <c r="B21" s="7" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>EXCEPTIONS</t>
         </is>
       </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="22" t="n"/>
+      <c r="E23" s="22" t="n"/>
+      <c r="F23" s="22" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>Exceptions</t>
         </is>
@@ -779,10 +855,14 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="52" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -806,33 +886,41 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BANK STATEMENT SIDE</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="23" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Balance per Bank Statement</t>
         </is>
       </c>
-      <c r="D6" s="7" t="n">
+      <c r="D6" s="25" t="n">
         <v>1495500</v>
       </c>
     </row>
+    <row r="7"/>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="24" t="inlineStr">
         <is>
           <t>Add: Deposits in Transit (in book, not yet on bank statement)</t>
         </is>
       </c>
+      <c r="B8" s="22" t="n"/>
+      <c r="C8" s="22" t="n"/>
+      <c r="D8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-30  CRJ-013  Capital introduced</t>
         </is>
@@ -843,25 +931,35 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="26" t="inlineStr">
         <is>
           <t>Total Deposits in Transit</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="B10" s="10" t="n"/>
+      <c r="C10" s="10" t="n"/>
+      <c r="D10" s="14" t="n">
         <v>500000</v>
       </c>
-    </row>
+      <c r="E10" s="10" t="n"/>
+      <c r="F10" s="10" t="n"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+    </row>
+    <row r="11"/>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="24" t="inlineStr">
         <is>
           <t>Less: Outstanding Cheques (in book, not yet cleared by bank)</t>
         </is>
       </c>
+      <c r="B12" s="22" t="n"/>
+      <c r="C12" s="22" t="n"/>
+      <c r="D12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-30  CPJ-015  Owner drawings</t>
         </is>
@@ -873,7 +971,7 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-31  PAY-004  Salaries - delivery</t>
         </is>
@@ -884,34 +982,46 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="10" t="inlineStr">
+      <c r="A15" s="26" t="inlineStr">
         <is>
           <t>Total Outstanding Cheques</t>
         </is>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="B15" s="10" t="n"/>
+      <c r="C15" s="10" t="n"/>
+      <c r="D15" s="14" t="n">
         <v>-560000</v>
       </c>
-    </row>
+      <c r="E15" s="10" t="n"/>
+      <c r="F15" s="10" t="n"/>
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n"/>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" s="13" t="inlineStr">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>ADJUSTED BANK BALANCE</t>
         </is>
       </c>
-      <c r="D17" s="14" t="n">
+      <c r="D17" s="7" t="n">
         <v>1435500</v>
       </c>
     </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="24" t="inlineStr">
         <is>
           <t>CASH BOOK SIDE</t>
         </is>
       </c>
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="22" t="n"/>
+      <c r="D20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Balance per Cash Book</t>
         </is>
@@ -920,16 +1030,20 @@
         <v>1438500</v>
       </c>
     </row>
+    <row r="22"/>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="24" t="inlineStr">
         <is>
           <t>Add: Bank Credits not yet in Cash Book</t>
         </is>
       </c>
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="22" t="n"/>
+      <c r="D23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-31  INT-001  Bank interest earned</t>
         </is>
@@ -940,25 +1054,35 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="10" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Total Bank Credits not in Book</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="14" t="n">
         <v>15000</v>
       </c>
-    </row>
+      <c r="E25" s="10" t="n"/>
+      <c r="F25" s="10" t="n"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n"/>
+    </row>
+    <row r="26"/>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="24" t="inlineStr">
         <is>
           <t>Less: Bank Debits not yet in Cash Book</t>
         </is>
       </c>
+      <c r="B27" s="22" t="n"/>
+      <c r="C27" s="22" t="n"/>
+      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n"/>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-28  DIRECT-01  Software subscription (auto-debit)</t>
         </is>
@@ -969,37 +1093,47 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="10" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Total Bank Debits not in Book</t>
         </is>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="14" t="n">
         <v>-18000</v>
       </c>
-    </row>
+      <c r="E29" s="10" t="n"/>
+      <c r="F29" s="10" t="n"/>
+      <c r="G29" s="10" t="n"/>
+      <c r="H29" s="10" t="n"/>
+    </row>
+    <row r="30"/>
     <row r="31">
-      <c r="A31" s="13" t="inlineStr">
+      <c r="A31" s="8" t="inlineStr">
         <is>
           <t>ADJUSTED CASH BOOK BALANCE</t>
         </is>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="7" t="n">
         <v>1435500</v>
       </c>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
-      <c r="A34" s="15" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
         <is>
           <t>Difference (must be ZERO)</t>
         </is>
       </c>
-      <c r="D34" s="16" t="n">
+      <c r="D34" s="27" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="8" t="inlineStr">
         <is>
           <t>RECONCILED</t>
         </is>
@@ -1031,15 +1165,15 @@
   <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2414,13 +2548,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2501,14 +2635,20 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="inlineStr">
+      <c r="A7" s="26" t="inlineStr">
         <is>
           <t>Total Outstanding Cheques</t>
         </is>
       </c>
-      <c r="B7" s="19" t="n">
+      <c r="B7" s="28" t="n">
         <v>-560000</v>
       </c>
+      <c r="C7" s="10" t="n"/>
+      <c r="D7" s="13" t="n"/>
+      <c r="E7" s="10" t="n"/>
+      <c r="F7" s="10" t="n"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2530,13 +2670,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2597,14 +2737,20 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="inlineStr">
+      <c r="A6" s="26" t="inlineStr">
         <is>
           <t>Total Deposits in Transit</t>
         </is>
       </c>
-      <c r="B6" s="14" t="n">
+      <c r="B6" s="28" t="n">
         <v>500000</v>
       </c>
+      <c r="C6" s="10" t="n"/>
+      <c r="D6" s="13" t="n"/>
+      <c r="E6" s="10" t="n"/>
+      <c r="F6" s="10" t="n"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2625,14 +2771,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2683,11 +2829,16 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="24" t="inlineStr">
         <is>
           <t>BANK CREDITS (deposits not in cash book)</t>
         </is>
       </c>
+      <c r="B5" s="22" t="n"/>
+      <c r="C5" s="22" t="n"/>
+      <c r="D5" s="22" t="n"/>
+      <c r="E5" s="22" t="n"/>
+      <c r="F5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2720,11 +2871,16 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="24" t="inlineStr">
         <is>
           <t>BANK DEBITS (withdrawals not in cash book)</t>
         </is>
       </c>
+      <c r="B7" s="22" t="n"/>
+      <c r="C7" s="22" t="n"/>
+      <c r="D7" s="22" t="n"/>
+      <c r="E7" s="22" t="n"/>
+      <c r="F7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2777,16 +2933,16 @@
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2960,36 +3116,37 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="inlineStr">
+      <c r="A8" s="26" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n">
+      <c r="B8" s="11" t="n"/>
+      <c r="C8" s="11" t="n"/>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="11" t="n"/>
+      <c r="F8" s="28" t="n">
         <v>33000</v>
       </c>
       <c r="G8" s="14" t="n"/>
-      <c r="H8" s="14" t="n"/>
-      <c r="I8" s="14" t="n">
+      <c r="H8" s="11" t="n"/>
+      <c r="I8" s="28" t="n">
         <v>33000</v>
       </c>
+      <c r="J8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="20" t="inlineStr">
+      <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Double-Entry Check</t>
         </is>
       </c>
-      <c r="F9" s="20" t="inlineStr">
+      <c r="F9" s="8" t="inlineStr">
         <is>
           <t>Dr = Cr?</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/accountant-skill/data/output/Jan2026/bank_reconciliation_Jan2026.xlsx
+++ b/accountant-skill/data/output/Jan2026/bank_reconciliation_Jan2026.xlsx
@@ -116,7 +116,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -136,39 +136,11 @@
     <border>
       <bottom style="double"/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -216,26 +188,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -606,14 +558,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="36" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -644,28 +596,21 @@
           <t>RECONCILIATION STATUS</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="22" t="n"/>
-      <c r="G5" s="22" t="n"/>
-      <c r="H5" s="23" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="6" t="inlineStr">
         <is>
           <t>RECONCILED</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Difference</t>
         </is>
@@ -676,21 +621,14 @@
     </row>
     <row r="8"/>
     <row r="9">
-      <c r="A9" s="24" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>BALANCES</t>
         </is>
       </c>
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="22" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="22" t="n"/>
-      <c r="H9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Cash Book Closing Balance</t>
         </is>
@@ -700,7 +638,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Bank Statement Closing Balance</t>
         </is>
@@ -710,7 +648,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Adjusted Book Balance</t>
         </is>
@@ -720,7 +658,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Adjusted Bank Balance</t>
         </is>
@@ -731,96 +669,82 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>RECONCILING ITEMS</t>
         </is>
       </c>
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="22" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="22" t="n"/>
-      <c r="H15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Transactions Matched</t>
         </is>
       </c>
-      <c r="B16" s="7" t="n">
+      <c r="B16" s="8" t="n">
         <v>30</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Deposits in Transit</t>
         </is>
       </c>
-      <c r="B17" s="7" t="n">
+      <c r="B17" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Outstanding Cheques</t>
         </is>
       </c>
-      <c r="B18" s="7" t="n">
+      <c r="B18" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Bank Credits not in Book</t>
         </is>
       </c>
-      <c r="B19" s="7" t="n">
+      <c r="B19" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Bank Debits not in Book</t>
         </is>
       </c>
-      <c r="B20" s="7" t="n">
+      <c r="B20" s="8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Adjusting Entries Required</t>
         </is>
       </c>
-      <c r="B21" s="7" t="n">
+      <c r="B21" s="8" t="n">
         <v>2</v>
       </c>
     </row>
     <row r="22"/>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>EXCEPTIONS</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="22" t="n"/>
-      <c r="F23" s="22" t="n"/>
-      <c r="G23" s="22" t="n"/>
-      <c r="H23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Exceptions</t>
         </is>
@@ -855,14 +779,10 @@
   <dimension ref="A1:H36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="52" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -886,41 +806,33 @@
         </is>
       </c>
     </row>
-    <row r="4"/>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BANK STATEMENT SIDE</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="23" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Balance per Bank Statement</t>
         </is>
       </c>
-      <c r="D6" s="25" t="n">
+      <c r="D6" s="7" t="n">
         <v>1495500</v>
       </c>
     </row>
-    <row r="7"/>
     <row r="8">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>Add: Deposits in Transit (in book, not yet on bank statement)</t>
         </is>
       </c>
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="22" t="n"/>
-      <c r="D8" s="23" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="n"/>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-30  CRJ-013  Capital introduced</t>
         </is>
@@ -931,35 +843,25 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="26" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Total Deposits in Transit</t>
         </is>
       </c>
-      <c r="B10" s="10" t="n"/>
-      <c r="C10" s="10" t="n"/>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="11" t="n">
         <v>500000</v>
       </c>
-      <c r="E10" s="10" t="n"/>
-      <c r="F10" s="10" t="n"/>
-      <c r="G10" s="10" t="n"/>
-      <c r="H10" s="10" t="n"/>
-    </row>
-    <row r="11"/>
+    </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>Less: Outstanding Cheques (in book, not yet cleared by bank)</t>
         </is>
       </c>
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="23" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="9" t="n"/>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-30  CPJ-015  Owner drawings</t>
         </is>
@@ -971,7 +873,7 @@
     </row>
     <row r="14">
       <c r="A14" s="9" t="n"/>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-31  PAY-004  Salaries - delivery</t>
         </is>
@@ -982,46 +884,34 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="26" t="inlineStr">
+      <c r="A15" s="10" t="inlineStr">
         <is>
           <t>Total Outstanding Cheques</t>
         </is>
       </c>
-      <c r="B15" s="10" t="n"/>
-      <c r="C15" s="10" t="n"/>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="11" t="n">
         <v>-560000</v>
       </c>
-      <c r="E15" s="10" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="10" t="n"/>
-    </row>
-    <row r="16"/>
+    </row>
     <row r="17">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="13" t="inlineStr">
         <is>
           <t>ADJUSTED BANK BALANCE</t>
         </is>
       </c>
-      <c r="D17" s="7" t="n">
+      <c r="D17" s="14" t="n">
         <v>1435500</v>
       </c>
     </row>
-    <row r="18"/>
-    <row r="19"/>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>CASH BOOK SIDE</t>
         </is>
       </c>
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Balance per Cash Book</t>
         </is>
@@ -1030,20 +920,16 @@
         <v>1438500</v>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>Add: Bank Credits not yet in Cash Book</t>
         </is>
       </c>
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="22" t="n"/>
-      <c r="D23" s="23" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="9" t="n"/>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-31  INT-001  Bank interest earned</t>
         </is>
@@ -1054,35 +940,25 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="26" t="inlineStr">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>Total Bank Credits not in Book</t>
         </is>
       </c>
-      <c r="B25" s="10" t="n"/>
-      <c r="C25" s="10" t="n"/>
-      <c r="D25" s="14" t="n">
+      <c r="D25" s="11" t="n">
         <v>15000</v>
       </c>
-      <c r="E25" s="10" t="n"/>
-      <c r="F25" s="10" t="n"/>
-      <c r="G25" s="10" t="n"/>
-      <c r="H25" s="10" t="n"/>
-    </row>
-    <row r="26"/>
+    </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>Less: Bank Debits not yet in Cash Book</t>
         </is>
       </c>
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="23" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="9" t="n"/>
-      <c r="B28" s="8" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t xml:space="preserve">  2026-01-28  DIRECT-01  Software subscription (auto-debit)</t>
         </is>
@@ -1093,47 +969,37 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="26" t="inlineStr">
+      <c r="A29" s="10" t="inlineStr">
         <is>
           <t>Total Bank Debits not in Book</t>
         </is>
       </c>
-      <c r="B29" s="10" t="n"/>
-      <c r="C29" s="10" t="n"/>
-      <c r="D29" s="14" t="n">
+      <c r="D29" s="11" t="n">
         <v>-18000</v>
       </c>
-      <c r="E29" s="10" t="n"/>
-      <c r="F29" s="10" t="n"/>
-      <c r="G29" s="10" t="n"/>
-      <c r="H29" s="10" t="n"/>
-    </row>
-    <row r="30"/>
+    </row>
     <row r="31">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>ADJUSTED CASH BOOK BALANCE</t>
         </is>
       </c>
-      <c r="D31" s="7" t="n">
+      <c r="D31" s="14" t="n">
         <v>1435500</v>
       </c>
     </row>
-    <row r="32"/>
-    <row r="33"/>
     <row r="34">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="15" t="inlineStr">
         <is>
           <t>Difference (must be ZERO)</t>
         </is>
       </c>
-      <c r="D34" s="27" t="n">
+      <c r="D34" s="16" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="35"/>
     <row r="36">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>RECONCILED</t>
         </is>
@@ -1165,15 +1031,15 @@
   <dimension ref="A1:I34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
     <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2548,13 +2414,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2635,20 +2501,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="26" t="inlineStr">
+      <c r="A7" s="13" t="inlineStr">
         <is>
           <t>Total Outstanding Cheques</t>
         </is>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="19" t="n">
         <v>-560000</v>
       </c>
-      <c r="C7" s="10" t="n"/>
-      <c r="D7" s="13" t="n"/>
-      <c r="E7" s="10" t="n"/>
-      <c r="F7" s="10" t="n"/>
-      <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2670,13 +2530,13 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2737,20 +2597,14 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="26" t="inlineStr">
+      <c r="A6" s="13" t="inlineStr">
         <is>
           <t>Total Deposits in Transit</t>
         </is>
       </c>
-      <c r="B6" s="28" t="n">
+      <c r="B6" s="14" t="n">
         <v>500000</v>
       </c>
-      <c r="C6" s="10" t="n"/>
-      <c r="D6" s="13" t="n"/>
-      <c r="E6" s="10" t="n"/>
-      <c r="F6" s="10" t="n"/>
-      <c r="G6" s="10" t="n"/>
-      <c r="H6" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2771,14 +2625,14 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
     <col width="43" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2829,16 +2683,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>BANK CREDITS (deposits not in cash book)</t>
         </is>
       </c>
-      <c r="B5" s="22" t="n"/>
-      <c r="C5" s="22" t="n"/>
-      <c r="D5" s="22" t="n"/>
-      <c r="E5" s="22" t="n"/>
-      <c r="F5" s="23" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
@@ -2871,16 +2720,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>BANK DEBITS (withdrawals not in cash book)</t>
         </is>
       </c>
-      <c r="B7" s="22" t="n"/>
-      <c r="C7" s="22" t="n"/>
-      <c r="D7" s="22" t="n"/>
-      <c r="E7" s="22" t="n"/>
-      <c r="F7" s="23" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
@@ -2933,16 +2777,16 @@
   <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
     <col width="36" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
     <col width="17" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3116,37 +2960,36 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="26" t="inlineStr">
+      <c r="A8" s="13" t="inlineStr">
         <is>
           <t>Totals</t>
         </is>
       </c>
-      <c r="B8" s="11" t="n"/>
-      <c r="C8" s="11" t="n"/>
-      <c r="D8" s="11" t="n"/>
-      <c r="E8" s="11" t="n"/>
-      <c r="F8" s="28" t="n">
+      <c r="B8" s="14" t="n"/>
+      <c r="C8" s="14" t="n"/>
+      <c r="D8" s="14" t="n"/>
+      <c r="E8" s="14" t="n"/>
+      <c r="F8" s="14" t="n">
         <v>33000</v>
       </c>
       <c r="G8" s="14" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="28" t="n">
+      <c r="H8" s="14" t="n"/>
+      <c r="I8" s="14" t="n">
         <v>33000</v>
       </c>
-      <c r="J8" s="13" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="20" t="inlineStr">
         <is>
           <t>Double-Entry Check</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="20" t="inlineStr">
         <is>
           <t>Dr = Cr?</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
+      <c r="G9" s="21" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
